--- a/artfynd/A 3676-2024 artfynd.xlsx
+++ b/artfynd/A 3676-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3676-2024 artfynd.xlsx
+++ b/artfynd/A 3676-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114718447</v>
+        <v>114702402</v>
       </c>
       <c r="B10" t="n">
-        <v>97528</v>
+        <v>57597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,46 +1552,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finsjölund, Finsjö, Sm</t>
+          <t>Finsjölund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573142</v>
+        <v>573360</v>
       </c>
       <c r="R10" t="n">
-        <v>6334324</v>
+        <v>6334360</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1621,47 +1619,36 @@
           <t>2024-02-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-02-17</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114718454</v>
+        <v>114718447</v>
       </c>
       <c r="B11" t="n">
         <v>97528</v>
@@ -1696,7 +1683,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1705,14 +1692,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnsjölund, Finsjö, Sm</t>
+          <t>Finsjölund, Finsjö, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573145</v>
+        <v>573142</v>
       </c>
       <c r="R11" t="n">
-        <v>6334358</v>
+        <v>6334324</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114718462</v>
+        <v>114718454</v>
       </c>
       <c r="B12" t="n">
         <v>97528</v>
@@ -1817,7 +1804,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1826,14 +1813,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finsjölund, Finsjö, Sm</t>
+          <t>Finnsjölund, Finsjö, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573148</v>
+        <v>573145</v>
       </c>
       <c r="R12" t="n">
-        <v>6334351</v>
+        <v>6334358</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,6 +1887,251 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114718462</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Finsjölund, Finsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573148</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6334351</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114718810</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Finsjölund, Finsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>573142</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6334324</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
